--- a/Utilities/Catalogue/integration-details.xlsx
+++ b/Utilities/Catalogue/integration-details.xlsx
@@ -25,22 +25,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regulatory, Market &amp; Environmen" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Power Generation &amp; SCADA Operat'!$A$1:$I$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Transmission Operations &amp; EMS'!$A$1:$I$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Substation Automation &amp; Protect'!$A$1:$I$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Distribution Grid &amp; ADMS'!$A$1:$I$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Water Treatment Plant Operation'!$A$1:$I$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Water Distribution Network Mana'!$A$1:$I$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Wastewater Collection &amp; Treatme'!$A$1:$I$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Metering &amp; Smart Grid'!$A$1:$I$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Customer Engagement &amp; Demand Re'!$A$1:$I$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Billing, CIS &amp; Revenue Manageme'!$A$1:$I$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Outage &amp; Workforce Management'!$A$1:$I$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Asset Management &amp; GIS'!$A$1:$I$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Enterprise Resource Planning'!$A$1:$I$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Cybersecurity &amp; Compliance'!$A$1:$I$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Data, Analytics &amp; AI'!$A$1:$I$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Regulatory, Market &amp; Environmen'!$A$1:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Power Generation &amp; SCADA Operat'!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Transmission Operations &amp; EMS'!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Substation Automation &amp; Protect'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Distribution Grid &amp; ADMS'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Water Treatment Plant Operation'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Water Distribution Network Mana'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Wastewater Collection &amp; Treatme'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Metering &amp; Smart Grid'!$A$1:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Customer Engagement &amp; Demand Re'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Billing, CIS &amp; Revenue Manageme'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Outage &amp; Workforce Management'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Asset Management &amp; GIS'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Enterprise Resource Planning'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Cybersecurity &amp; Compliance'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Data, Analytics &amp; AI'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Regulatory, Market &amp; Environmen'!$A$1:$J$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -485,6 +485,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,6 +534,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -580,6 +586,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -627,6 +638,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -674,6 +690,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -721,6 +742,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -768,6 +794,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -815,6 +846,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -862,6 +898,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -909,6 +950,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -956,6 +1002,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1003,6 +1054,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1050,6 +1106,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1097,6 +1158,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1144,6 +1210,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1191,6 +1262,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1238,6 +1314,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1285,6 +1366,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1332,6 +1418,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1379,6 +1470,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1426,6 +1522,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1473,6 +1574,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1520,6 +1626,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1567,6 +1678,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1614,6 +1730,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1661,6 +1782,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1708,6 +1834,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1755,6 +1886,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1802,6 +1938,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1849,6 +1990,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1896,9 +2042,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I30"/>
+  <autoFilter ref="A1:J30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1909,7 +2060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1921,6 +2072,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1969,6 +2121,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2016,6 +2173,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2063,6 +2225,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2110,6 +2277,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2157,6 +2329,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2204,6 +2381,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2251,6 +2433,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2298,6 +2485,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2345,6 +2537,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2392,6 +2589,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2439,6 +2641,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2486,6 +2693,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2533,6 +2745,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2580,6 +2797,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2627,6 +2849,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2674,6 +2901,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2721,6 +2953,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2768,6 +3005,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2815,6 +3057,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2862,6 +3109,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2909,6 +3161,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2956,6 +3213,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3003,6 +3265,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3050,6 +3317,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -3097,6 +3369,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3144,6 +3421,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3191,6 +3473,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3238,6 +3525,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3285,9 +3577,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3298,7 +3595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3310,6 +3607,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3358,6 +3656,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3405,6 +3708,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3452,6 +3760,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3499,6 +3812,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>High-frequency near-real-time batch processing with minimal latency tolerance</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3546,6 +3864,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3593,6 +3916,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3640,6 +3968,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3687,6 +4020,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -3734,6 +4072,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3781,6 +4124,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3828,6 +4176,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3875,6 +4228,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3922,6 +4280,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3969,6 +4332,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -4016,6 +4384,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -4063,6 +4436,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4110,6 +4488,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4157,6 +4540,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4204,6 +4592,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4251,6 +4644,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4298,6 +4696,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4345,6 +4748,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4392,6 +4800,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4439,6 +4852,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4486,6 +4904,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4533,6 +4956,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -4580,6 +5008,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4627,6 +5060,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -4674,9 +5112,14 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4687,7 +5130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4699,6 +5142,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4747,6 +5191,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -4794,6 +5243,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4841,6 +5295,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Periodic near-real-time batch with data validation and transformation needs</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4888,6 +5347,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4935,6 +5399,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4982,6 +5451,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -5029,6 +5503,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -5076,6 +5555,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -5123,6 +5607,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -5170,6 +5659,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>High-frequency near-real-time batch processing with minimal latency tolerance</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -5217,6 +5711,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -5264,6 +5763,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -5311,6 +5815,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -5358,6 +5867,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -5405,6 +5919,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -5452,6 +5971,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -5499,6 +6023,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -5546,6 +6075,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -5593,6 +6127,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -5640,6 +6179,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -5687,6 +6231,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -5734,6 +6283,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5781,6 +6335,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5828,6 +6387,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5875,6 +6439,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5922,6 +6491,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5969,6 +6543,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -6016,6 +6595,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6063,9 +6647,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6076,7 +6665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6088,6 +6677,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6136,6 +6726,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6183,6 +6778,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6230,6 +6830,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -6277,6 +6882,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Periodic near-real-time batch with data validation and transformation needs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -6324,6 +6934,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -6371,6 +6986,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -6418,6 +7038,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -6465,6 +7090,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -6512,6 +7142,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -6559,6 +7194,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -6606,6 +7246,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -6653,6 +7298,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -6700,6 +7350,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -6747,6 +7402,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -6794,6 +7454,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Minimal near-real-time batch with basic data pass-through</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -6841,6 +7506,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -6888,6 +7558,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -6935,6 +7610,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -6982,6 +7662,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -7029,6 +7714,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>High-frequency near-real-time batch processing with minimal latency tolerance</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -7076,6 +7766,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -7123,6 +7818,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -7170,6 +7870,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -7217,6 +7922,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -7264,6 +7974,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -7311,6 +8026,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -7358,6 +8078,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -7405,6 +8130,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -7452,9 +8182,14 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7465,7 +8200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7477,6 +8212,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7525,6 +8261,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -7572,6 +8313,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -7619,6 +8365,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -7666,6 +8417,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -7713,6 +8469,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -7760,6 +8521,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -7807,6 +8573,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -7854,6 +8625,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -7901,6 +8677,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -7948,6 +8729,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -7995,6 +8781,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -8042,6 +8833,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -8089,6 +8885,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -8136,6 +8937,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -8183,6 +8989,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -8230,6 +9041,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -8277,6 +9093,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -8324,6 +9145,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -8371,6 +9197,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -8418,6 +9249,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -8465,6 +9301,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -8512,6 +9353,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -8559,6 +9405,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -8606,6 +9457,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -8653,6 +9509,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -8700,6 +9561,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -8747,6 +9613,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -8794,6 +9665,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -8841,9 +9717,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8854,7 +9735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8866,6 +9747,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8914,6 +9796,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -8961,6 +9848,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -9008,6 +9900,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -9055,6 +9952,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Periodic near-real-time batch with data validation and transformation needs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -9102,6 +10004,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -9149,6 +10056,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -9196,6 +10108,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -9243,6 +10160,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -9290,6 +10212,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -9337,6 +10264,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -9384,6 +10316,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -9431,6 +10368,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -9478,6 +10420,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -9525,6 +10472,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Periodic near-real-time batch with data validation and transformation needs</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -9572,6 +10524,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -9619,6 +10576,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -9666,6 +10628,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -9713,6 +10680,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -9760,6 +10732,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -9807,6 +10784,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -9854,6 +10836,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -9901,6 +10888,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -9948,6 +10940,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -9995,6 +10992,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -10042,6 +11044,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -10089,6 +11096,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Periodic near-real-time batch with data validation and transformation needs</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -10136,6 +11148,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -10183,6 +11200,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -10230,9 +11252,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10243,7 +11270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10255,6 +11282,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10303,6 +11331,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -10350,6 +11383,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -10397,6 +11435,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -10444,6 +11487,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -10491,6 +11539,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -10538,6 +11591,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -10585,6 +11643,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -10632,6 +11695,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -10679,6 +11747,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -10726,6 +11799,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -10773,6 +11851,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -10820,6 +11903,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -10867,6 +11955,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -10914,6 +12007,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -10961,6 +12059,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -11008,6 +12111,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -11055,6 +12163,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -11102,6 +12215,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -11149,6 +12267,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -11196,6 +12319,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -11243,6 +12371,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -11290,6 +12423,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -11337,6 +12475,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -11384,6 +12527,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -11431,6 +12579,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -11478,6 +12631,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -11525,6 +12683,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -11572,6 +12735,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Periodic near-real-time batch with data validation and transformation needs</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -11619,9 +12787,14 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11632,7 +12805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11644,6 +12817,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11692,6 +12866,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -11739,6 +12918,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -11786,6 +12970,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>High-frequency near-real-time batch processing with minimal latency tolerance</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -11833,6 +13022,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -11880,6 +13074,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>High-frequency near-real-time batch processing with minimal latency tolerance</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -11927,6 +13126,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -11974,6 +13178,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -12021,6 +13230,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -12068,6 +13282,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -12115,6 +13334,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>High-frequency near-real-time batch processing with minimal latency tolerance</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -12162,6 +13386,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>High-frequency near-real-time batch processing with minimal latency tolerance</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -12209,6 +13438,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -12256,6 +13490,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -12303,6 +13542,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -12350,6 +13594,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -12397,6 +13646,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -12444,6 +13698,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>High-frequency near-real-time batch processing with minimal latency tolerance</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -12491,6 +13750,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -12538,6 +13802,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Periodic near-real-time batch with data validation and transformation needs</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -12585,6 +13854,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -12632,6 +13906,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -12679,6 +13958,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -12726,6 +14010,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -12773,6 +14062,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -12820,6 +14114,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -12867,6 +14166,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -12914,6 +14218,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -12961,6 +14270,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -13008,6 +14322,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -13055,9 +14374,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I30"/>
+  <autoFilter ref="A1:J30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13068,7 +14392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13080,6 +14404,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13128,6 +14453,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -13175,6 +14505,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -13222,6 +14557,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -13269,6 +14609,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -13316,6 +14661,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -13363,6 +14713,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -13410,6 +14765,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -13457,6 +14817,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -13504,6 +14869,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -13551,6 +14921,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>High-frequency near-real-time batch processing with minimal latency tolerance</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -13598,6 +14973,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -13645,6 +15025,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -13692,6 +15077,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -13739,6 +15129,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Minimal near-real-time batch with basic data pass-through</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -13786,6 +15181,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -13833,6 +15233,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -13880,6 +15285,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -13927,6 +15337,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -13974,6 +15389,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -14021,6 +15441,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -14068,6 +15493,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -14115,6 +15545,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -14162,6 +15597,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -14209,6 +15649,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -14256,6 +15701,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -14303,6 +15753,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -14350,6 +15805,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -14397,6 +15857,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -14444,9 +15909,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14457,7 +15927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14469,6 +15939,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14517,6 +15988,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -14564,6 +16040,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -14611,6 +16092,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>High-frequency near-real-time batch processing with minimal latency tolerance</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -14658,6 +16144,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -14705,6 +16196,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -14752,6 +16248,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -14799,6 +16300,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Periodic near-real-time batch with data validation and transformation needs</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -14846,6 +16352,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -14893,6 +16404,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -14940,6 +16456,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -14987,6 +16508,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -15034,6 +16560,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -15081,6 +16612,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -15128,6 +16664,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -15175,6 +16716,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -15222,6 +16768,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -15269,6 +16820,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>High-frequency near-real-time batch processing with minimal latency tolerance</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -15316,6 +16872,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -15363,6 +16924,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -15410,6 +16976,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -15457,6 +17028,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -15504,6 +17080,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -15551,6 +17132,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -15598,6 +17184,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -15645,6 +17236,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Periodic near-real-time batch with data validation and transformation needs</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -15692,6 +17288,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Periodic near-real-time batch with data validation and transformation needs</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -15739,6 +17340,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -15786,6 +17392,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -15833,9 +17444,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15846,7 +17462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15858,6 +17474,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15906,6 +17523,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -15953,6 +17575,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -16000,6 +17627,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -16047,6 +17679,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -16094,6 +17731,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -16141,6 +17783,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -16188,6 +17835,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -16235,6 +17887,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -16282,6 +17939,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -16329,6 +17991,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -16376,6 +18043,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -16423,6 +18095,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -16470,6 +18147,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -16517,6 +18199,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -16564,6 +18251,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -16611,6 +18303,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -16658,6 +18355,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -16705,6 +18407,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -16752,6 +18459,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -16799,6 +18511,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -16846,6 +18563,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -16893,6 +18615,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -16940,6 +18667,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -16987,6 +18719,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -17034,6 +18771,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -17081,6 +18823,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -17128,6 +18875,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -17175,6 +18927,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -17222,9 +18979,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17235,7 +18997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17247,6 +19009,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17295,6 +19058,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -17342,6 +19110,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -17389,6 +19162,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -17436,6 +19214,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -17483,6 +19266,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -17530,6 +19318,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Periodic near-real-time batch with data validation and transformation needs</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -17577,6 +19370,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -17624,6 +19422,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -17671,6 +19474,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -17718,6 +19526,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -17765,6 +19578,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -17812,6 +19630,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -17859,6 +19682,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -17906,6 +19734,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -17953,6 +19786,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -18000,6 +19838,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -18047,6 +19890,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -18094,6 +19942,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -18141,6 +19994,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -18188,6 +20046,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -18235,6 +20098,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -18282,6 +20150,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -18329,6 +20202,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -18376,6 +20254,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -18423,6 +20306,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -18470,6 +20358,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -18517,6 +20410,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -18564,6 +20462,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -18611,9 +20514,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18624,7 +20532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18636,6 +20544,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18684,6 +20593,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -18731,6 +20645,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -18778,6 +20697,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -18825,6 +20749,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -18872,6 +20801,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -18919,6 +20853,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -18966,6 +20905,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -19013,6 +20957,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -19060,6 +21009,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -19107,6 +21061,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -19154,6 +21113,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -19201,6 +21165,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -19248,6 +21217,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -19295,6 +21269,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -19342,6 +21321,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -19389,6 +21373,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -19436,6 +21425,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -19483,6 +21477,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -19530,6 +21529,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -19577,6 +21581,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -19624,6 +21633,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -19671,6 +21685,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -19718,6 +21737,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -19765,6 +21789,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -19812,6 +21841,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -19859,6 +21893,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -19906,6 +21945,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -19953,6 +21997,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -20000,9 +22049,14 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20013,7 +22067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20025,6 +22079,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20073,6 +22128,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -20120,6 +22180,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -20167,6 +22232,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -20214,6 +22284,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -20261,6 +22336,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -20308,6 +22388,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -20355,6 +22440,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -20402,9 +22492,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I8"/>
+  <autoFilter ref="A1:J8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20415,7 +22510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20427,6 +22522,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20475,6 +22571,11 @@
           <t>Complexity</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Complexity Reason</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -20522,6 +22623,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -20569,6 +22675,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -20616,6 +22727,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -20663,6 +22779,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -20710,6 +22831,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -20757,6 +22883,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -20804,6 +22935,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -20851,6 +22987,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -20898,6 +23039,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Mission-critical event processing requiring guaranteed delivery, sequencing, and audit trail</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -20945,6 +23091,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Event-driven integration with intermediate complexity in event routing and state management</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -20992,6 +23143,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -21039,6 +23195,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -21086,6 +23247,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -21133,6 +23299,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Straightforward periodic data transfer with no real-time constraints</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -21180,6 +23351,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -21227,6 +23403,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -21274,6 +23455,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -21321,6 +23507,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -21368,6 +23559,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -21415,6 +23611,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Large-volume scheduled processing with data integrity validation and reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -21462,6 +23663,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled batch transfer requiring field mapping, validation, and exception handling</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -21509,6 +23715,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -21556,6 +23767,11 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Direct API integration with minimal transformation and single-system lookup</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -21603,6 +23819,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -21650,6 +23871,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -21697,6 +23923,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>OT/IT boundary crossing with sub-second latency and strict data fidelity requirements</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -21744,6 +23975,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>API integration requiring moderate transformation, error handling, and data reconciliation</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -21791,9 +24027,14 @@
           <t>Simple</t>
         </is>
       </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Simple event notification with fire-and-forget delivery semantics</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>